--- a/2025-2026 잉글랜드 프리미어리그.xlsx
+++ b/2025-2026 잉글랜드 프리미어리그.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -69148,7 +69148,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -71813,9 +71813,21 @@
           <t>2.37</t>
         </is>
       </c>
-      <c r="AY169" s="2" t="inlineStr"/>
-      <c r="AZ169" s="2" t="inlineStr"/>
-      <c r="BA169" s="2" t="inlineStr"/>
+      <c r="AY169" s="2" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="AZ169" s="2" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="BA169" s="2" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
       <c r="BB169" s="2" t="inlineStr">
         <is>
           <t>2.60</t>
@@ -73034,9 +73046,21 @@
           <t>3.30</t>
         </is>
       </c>
-      <c r="AY172" s="2" t="inlineStr"/>
-      <c r="AZ172" s="2" t="inlineStr"/>
-      <c r="BA172" s="2" t="inlineStr"/>
+      <c r="AY172" s="2" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="AZ172" s="2" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="BA172" s="2" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
       <c r="BB172" s="2" t="inlineStr">
         <is>
           <t>2.18</t>
